--- a/Scripts_Data/CFL_Results_REF.xlsx
+++ b/Scripts_Data/CFL_Results_REF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\simscape\demo\multibody\contact-forces-library\Scripts_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E4D30C-C1E6-478F-A3A0-D5722EC44EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DE20D2-0FAE-4493-AF12-DF14265E2CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="820" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="1635" windowWidth="26370" windowHeight="10005" tabRatio="820" firstSheet="17" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R16b_v3p6" sheetId="17" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="R24a_v5p0" sheetId="39" r:id="rId21"/>
     <sheet name="R24b_v5p0" sheetId="40" r:id="rId22"/>
     <sheet name="R25b_v5p0" sheetId="41" r:id="rId23"/>
+    <sheet name="R26a5p0" sheetId="42" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="219">
   <si>
     <t>#</t>
   </si>
@@ -707,6 +708,9 @@
   <si>
     <t>17-Dec-2025 18:38:30</t>
   </si>
+  <si>
+    <t>26.1.0.3203278 (R2026a)</t>
+  </si>
 </sst>
 </file>
 
@@ -32197,6 +32201,1955 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741743B2-BB6C-4955-93BB-70888D92D4BC}">
+  <dimension ref="A1:K56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="9.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="18">
+        <v>46132.813321759262</v>
+      </c>
+      <c r="G1" s="18"/>
+      <c r="H1" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="21"/>
+      <c r="H2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="16">
+        <v>6</v>
+      </c>
+      <c r="D4" s="17">
+        <v>2872</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0.505</v>
+      </c>
+      <c r="F4" s="17">
+        <v>2872</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2872</v>
+      </c>
+      <c r="I4" s="17">
+        <v>0.152</v>
+      </c>
+      <c r="J4" s="17">
+        <v>2872</v>
+      </c>
+      <c r="K4" s="17">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="10">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>743</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="F5" s="3">
+        <v>998</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>781</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1045</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>491</v>
+      </c>
+      <c r="E6" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>526</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>513</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>553</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="10">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4218</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.411</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4776</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.4119999999999999</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5370</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.556</v>
+      </c>
+      <c r="J7" s="3">
+        <v>6259</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2.0670000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2356</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2828</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2579</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3077</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>775</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>528</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>854</v>
+      </c>
+      <c r="I9" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>541</v>
+      </c>
+      <c r="K9" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>220</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F10" s="3">
+        <v>225</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>235</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>235</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="10">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>24447</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.9239999999999999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>51846</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5.6589999999999998</v>
+      </c>
+      <c r="H11" s="3">
+        <v>26130</v>
+      </c>
+      <c r="I11" s="3">
+        <v>4.1859999999999999</v>
+      </c>
+      <c r="J11" s="3">
+        <v>55776</v>
+      </c>
+      <c r="K11" s="3">
+        <v>12.129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="10">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1137</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1137</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1137</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1137</v>
+      </c>
+      <c r="K12" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="10">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1313</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1401</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1398</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1490</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="10">
+        <v>45</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5550</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5550</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5550</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.253</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5550</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.28299999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3">
+        <v>821</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="F15" s="3">
+        <v>938</v>
+      </c>
+      <c r="G15" s="3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>864</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>980</v>
+      </c>
+      <c r="K15" s="3">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="10">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1450</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1516</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.109</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1501</v>
+      </c>
+      <c r="I16" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1562</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="10">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5901</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.284</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6071</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="H17" s="3">
+        <v>6216</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6507</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.80200000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>293</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.109</v>
+      </c>
+      <c r="F18" s="3">
+        <v>323</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>317</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="J18" s="3">
+        <v>345</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="10">
+        <v>30</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3564</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="F19" s="3">
+        <v>3636</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="H19" s="3">
+        <v>3609</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.437</v>
+      </c>
+      <c r="J19" s="3">
+        <v>3751</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="10">
+        <v>50</v>
+      </c>
+      <c r="D20" s="3">
+        <v>6943</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.1180000000000001</v>
+      </c>
+      <c r="F20" s="3">
+        <v>7054</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="H20" s="3">
+        <v>164459</v>
+      </c>
+      <c r="I20" s="3">
+        <v>11.882999999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>175049</v>
+      </c>
+      <c r="K20" s="3">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="10">
+        <v>30</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3444</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3602</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.248</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3940</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J21" s="3">
+        <v>4310</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="10">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1166</v>
+      </c>
+      <c r="E22" s="10">
+        <v>3.2330000000000001</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1166</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3.008</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1166</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.6440000000000001</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1166</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2.5950000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="10">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2720</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1.827</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2783</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="H23" s="3">
+        <v>3463</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3610</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="10">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>147</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="F24" s="3">
+        <v>147</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>147</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="J24" s="3">
+        <v>147</v>
+      </c>
+      <c r="K24" s="3">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="10">
+        <v>30</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4818</v>
+      </c>
+      <c r="E25" s="10">
+        <v>3.0979999999999999</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5227</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3.0720000000000001</v>
+      </c>
+      <c r="H25" s="3">
+        <v>4835</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.8540000000000001</v>
+      </c>
+      <c r="J25" s="3">
+        <v>5305</v>
+      </c>
+      <c r="K25" s="3">
+        <v>3.1549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="10">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3">
+        <v>13445</v>
+      </c>
+      <c r="E26" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13741</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.47</v>
+      </c>
+      <c r="H26" s="3">
+        <v>17921</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="J26" s="3">
+        <v>18604</v>
+      </c>
+      <c r="K26" s="3">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="10">
+        <v>20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3402</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1.7709999999999999</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3938</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1.6639999999999999</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3538</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1.4430000000000001</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4199</v>
+      </c>
+      <c r="K27" s="3">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>941</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1018</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0.108</v>
+      </c>
+      <c r="H28" s="3">
+        <v>967</v>
+      </c>
+      <c r="I28" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1070</v>
+      </c>
+      <c r="K28" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="10">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>757</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.151</v>
+      </c>
+      <c r="F29" s="3">
+        <v>847</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H29" s="3">
+        <v>792</v>
+      </c>
+      <c r="I29" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="J29" s="3">
+        <v>895</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="10">
+        <v>20</v>
+      </c>
+      <c r="D30" s="3">
+        <v>10374</v>
+      </c>
+      <c r="E30" s="10">
+        <v>7.6449999999999996</v>
+      </c>
+      <c r="F30" s="3">
+        <v>12258</v>
+      </c>
+      <c r="G30" s="3">
+        <v>13.021000000000001</v>
+      </c>
+      <c r="H30" s="3">
+        <v>11929</v>
+      </c>
+      <c r="I30" s="3">
+        <v>11.035</v>
+      </c>
+      <c r="J30" s="3">
+        <v>13366</v>
+      </c>
+      <c r="K30" s="3">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="10">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3">
+        <v>878</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="F31" s="3">
+        <v>917</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0.159</v>
+      </c>
+      <c r="H31" s="3">
+        <v>868</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J31" s="3">
+        <v>950</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="10">
+        <v>20</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2434</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1.4510000000000001</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5466</v>
+      </c>
+      <c r="G32" s="3">
+        <v>5.069</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2513</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6265</v>
+      </c>
+      <c r="K32" s="3">
+        <v>5.915</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="10">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2684</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4063</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="H33" s="3">
+        <v>3055</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="J33" s="3">
+        <v>4462</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0.70699999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="10">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
+        <v>472</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.755</v>
+      </c>
+      <c r="F34" s="3">
+        <v>887</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H34" s="3">
+        <v>511</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.112</v>
+      </c>
+      <c r="J34" s="3">
+        <v>856</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0.41299999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="10">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1735</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3261</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1.375</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1748</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3277</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.871</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="10">
+        <v>36</v>
+      </c>
+      <c r="D36" s="3">
+        <v>10291</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="F36" s="3">
+        <v>16024</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3.3410000000000002</v>
+      </c>
+      <c r="H36" s="3">
+        <v>10364</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="J36" s="3">
+        <v>16354</v>
+      </c>
+      <c r="K36" s="3">
+        <v>3.5369999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="10">
+        <v>48</v>
+      </c>
+      <c r="D37" s="3">
+        <v>6519</v>
+      </c>
+      <c r="E37" s="10">
+        <v>1.089</v>
+      </c>
+      <c r="F37" s="3">
+        <v>10972</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1.8480000000000001</v>
+      </c>
+      <c r="H37" s="3">
+        <v>6644</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="J37" s="3">
+        <v>10995</v>
+      </c>
+      <c r="K37" s="3">
+        <v>1.873</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>35</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="10">
+        <v>36</v>
+      </c>
+      <c r="D38" s="3">
+        <v>4176</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1.282</v>
+      </c>
+      <c r="F38" s="3">
+        <v>4686</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="H38" s="3">
+        <v>4245</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="J38" s="3">
+        <v>4750</v>
+      </c>
+      <c r="K38" s="3">
+        <v>1.1180000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>36</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="10">
+        <v>40</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2520</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3058</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0.317</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2633</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3070</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0.60599999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="10">
+        <v>36</v>
+      </c>
+      <c r="D40" s="3">
+        <v>4113</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1.569</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4559</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="H40" s="3">
+        <v>4237</v>
+      </c>
+      <c r="I40" s="3">
+        <v>1.276</v>
+      </c>
+      <c r="J40" s="3">
+        <v>4624</v>
+      </c>
+      <c r="K40" s="3">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>38</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="10">
+        <v>36</v>
+      </c>
+      <c r="D41" s="3">
+        <v>4597</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1.3280000000000001</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4566</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.0469999999999999</v>
+      </c>
+      <c r="H41" s="3">
+        <v>4746</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1.01</v>
+      </c>
+      <c r="J41" s="3">
+        <v>4613</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1.038</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="10">
+        <v>40</v>
+      </c>
+      <c r="D42" s="3">
+        <v>6021</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6493</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="H42" s="3">
+        <v>6384</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="J42" s="3">
+        <v>6783</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0.76700000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="10">
+        <v>10</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1396</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1498</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1417</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0.223</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1473</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="10">
+        <v>24</v>
+      </c>
+      <c r="D44" s="3">
+        <v>7582</v>
+      </c>
+      <c r="E44" s="10">
+        <v>2.4060000000000001</v>
+      </c>
+      <c r="F44" s="3">
+        <v>6881</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3.032</v>
+      </c>
+      <c r="H44" s="3">
+        <v>8314</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="J44" s="3">
+        <v>7104</v>
+      </c>
+      <c r="K44" s="3">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="10">
+        <v>30</v>
+      </c>
+      <c r="D45" s="3">
+        <v>4097</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1.448</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4162</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1.073</v>
+      </c>
+      <c r="H45" s="3">
+        <v>4041</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="J45" s="3">
+        <v>4185</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1.1579999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="10">
+        <v>30</v>
+      </c>
+      <c r="D46" s="3">
+        <v>4854</v>
+      </c>
+      <c r="E46" s="10">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4854</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2.3239999999999998</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4854</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2.2709999999999999</v>
+      </c>
+      <c r="J46" s="3">
+        <v>4854</v>
+      </c>
+      <c r="K46" s="3">
+        <v>2.3860000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>44</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="10">
+        <v>50</v>
+      </c>
+      <c r="D47" s="3">
+        <v>6109</v>
+      </c>
+      <c r="E47" s="10">
+        <v>3.2970000000000002</v>
+      </c>
+      <c r="F47" s="3">
+        <v>9169</v>
+      </c>
+      <c r="G47" s="3">
+        <v>5.0709999999999997</v>
+      </c>
+      <c r="H47" s="3">
+        <v>6004</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2.7269999999999999</v>
+      </c>
+      <c r="J47" s="3">
+        <v>9357</v>
+      </c>
+      <c r="K47" s="3">
+        <v>5.1749999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>45</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="10">
+        <v>33.72</v>
+      </c>
+      <c r="D48" s="3">
+        <v>4718</v>
+      </c>
+      <c r="E48" s="10">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="10">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="D49" s="3">
+        <v>4610</v>
+      </c>
+      <c r="E49" s="10">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>47</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="10">
+        <v>59.18</v>
+      </c>
+      <c r="D50" s="3">
+        <v>7916</v>
+      </c>
+      <c r="E50" s="10">
+        <v>3.9079999999999999</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="10">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="D51" s="3">
+        <v>5541</v>
+      </c>
+      <c r="E51" s="10">
+        <v>3.1779999999999999</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>49</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="10">
+        <v>34.64</v>
+      </c>
+      <c r="D52" s="3">
+        <v>4821</v>
+      </c>
+      <c r="E52" s="10">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="2">
+        <v>41.11</v>
+      </c>
+      <c r="D53" s="2">
+        <v>5858</v>
+      </c>
+      <c r="E53" s="10">
+        <v>4.3890000000000002</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>51</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="2">
+        <v>41.28</v>
+      </c>
+      <c r="D54" s="2">
+        <v>6036</v>
+      </c>
+      <c r="E54" s="10">
+        <v>3.7370000000000001</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>52</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="2">
+        <v>45.26</v>
+      </c>
+      <c r="D55" s="2">
+        <v>6345</v>
+      </c>
+      <c r="E55" s="10">
+        <v>5.7119999999999997</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>53</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2">
+        <v>27.73</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5172</v>
+      </c>
+      <c r="E56" s="10">
+        <v>4.33</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K51"/>
@@ -45176,23 +47129,64 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e7c50fe4-4c86-4d33-a0d3-ad29cfb7378a" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45342,59 +47336,10 @@
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e7c50fe4-4c86-4d33-a0d3-ad29cfb7378a" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19CAB08D-0D2F-4FAA-AD38-9A4550C5EE6B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07114D79-96C5-443E-AAB8-EBD3F08587B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -45410,10 +47355,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7E9F9B4-63C4-4A63-ABAD-3E68140B52AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE19BB6F-0BDA-4FED-9C87-C1B27317A152}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19CAB08D-0D2F-4FAA-AD38-9A4550C5EE6B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45437,9 +47390,9 @@
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7E9F9B4-63C4-4A63-ABAD-3E68140B52AA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE19BB6F-0BDA-4FED-9C87-C1B27317A152}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>